--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_15/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_15/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>61.09</v>
+        <v>63.43</v>
       </c>
       <c r="D2" t="n">
-        <v>18.32</v>
+        <v>17.49</v>
       </c>
       <c r="E2" t="n">
-        <v>29.98</v>
+        <v>27.57</v>
       </c>
       <c r="F2" t="n">
-        <v>40.27</v>
+        <v>41.79</v>
       </c>
       <c r="G2" t="n">
-        <v>45.26</v>
+        <v>48.73</v>
       </c>
       <c r="H2" t="n">
-        <v>55.82</v>
+        <v>59.42</v>
       </c>
       <c r="I2" t="n">
-        <v>73.67</v>
+        <v>77.42</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>59.73</v>
+        <v>58.21</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>47.37</v>
+        <v>45.66</v>
       </c>
       <c r="D3" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="F3" t="n">
-        <v>46.07</v>
+        <v>45.5</v>
       </c>
       <c r="G3" t="n">
-        <v>47.49</v>
+        <v>45.5</v>
       </c>
       <c r="H3" t="n">
-        <v>47.49</v>
+        <v>45.51</v>
       </c>
       <c r="I3" t="n">
-        <v>47.5</v>
+        <v>45.56</v>
       </c>
       <c r="J3" t="n">
-        <v>47.77</v>
+        <v>46.58</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>8.73</v>
+        <v>8.18</v>
       </c>
       <c r="D4" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="E4" t="n">
-        <v>15.88</v>
+        <v>16.22</v>
       </c>
       <c r="F4" t="n">
-        <v>5.03</v>
+        <v>5.71</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9</v>
+        <v>6.55</v>
       </c>
       <c r="H4" t="n">
-        <v>9.43</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>9.82</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>10.12</v>
+        <v>9.75</v>
       </c>
       <c r="K4" t="n">
-        <v>5.09</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>168.55</v>
+        <v>110.25</v>
       </c>
       <c r="D5" t="n">
-        <v>17.97</v>
+        <v>18.58</v>
       </c>
       <c r="E5" t="n">
-        <v>10.66</v>
+        <v>16.86</v>
       </c>
       <c r="F5" t="n">
-        <v>138.39</v>
+        <v>71.47</v>
       </c>
       <c r="G5" t="n">
-        <v>154.45</v>
+        <v>106.1</v>
       </c>
       <c r="H5" t="n">
-        <v>160.74</v>
+        <v>116.42</v>
       </c>
       <c r="I5" t="n">
-        <v>183.64</v>
+        <v>121.76</v>
       </c>
       <c r="J5" t="n">
-        <v>198.76</v>
+        <v>137.69</v>
       </c>
       <c r="K5" t="n">
-        <v>60.37</v>
+        <v>66.22</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="D6" t="n">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="E6" t="n">
-        <v>25.01</v>
+        <v>22.63</v>
       </c>
       <c r="F6" t="n">
-        <v>2.29</v>
+        <v>2.78</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91</v>
+        <v>3.01</v>
       </c>
       <c r="H6" t="n">
-        <v>3.98</v>
+        <v>4.37</v>
       </c>
       <c r="I6" t="n">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
   </sheetData>
